--- a/output/pdf_financials_xlsx/MMY.xlsx
+++ b/output/pdf_financials_xlsx/MMY.xlsx
@@ -706,19 +706,19 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.028131</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.104946</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.213</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.775</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.892</v>
       </c>
     </row>
     <row r="13">
@@ -1109,19 +1109,19 @@
         <v>-6.996867</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.04062</v>
+        <v>-3.068751</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>31.231583</v>
+        <v>31.126637</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>59.585</v>
+        <v>59.372</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>33.365</v>
+        <v>32.59</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.85</v>
+        <v>-2.742</v>
       </c>
     </row>
     <row r="28">
@@ -1159,19 +1159,19 @@
         <v>-6.996867</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.04062</v>
+        <v>-3.068751</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>31.231583</v>
+        <v>31.126637</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>63.501</v>
+        <v>63.288</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>43.982</v>
+        <v>43.207</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>7.371</v>
+        <v>6.479</v>
       </c>
     </row>
     <row r="30">
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>72.21881251189134</v>
+        <v>71.97613907782707</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>102.903952421851</v>
+        <v>102.5587839699234</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>48.18572242429554</v>
+        <v>47.33664928349183</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>15.17197373566886</v>
+        <v>13.33594055533829</v>
       </c>
     </row>
     <row r="31">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -14750,7 +14750,7 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">

--- a/output/pdf_financials_xlsx/MMY.xlsx
+++ b/output/pdf_financials_xlsx/MMY.xlsx
@@ -3275,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.021</v>
       </c>
       <c r="G112" s="3" t="n">
         <v>0</v>
@@ -10746,7 +10746,11 @@
           <t>Proceeds from disposal of plant and equipment</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MMY.xlsx
+++ b/output/pdf_financials_xlsx/MMY.xlsx
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>0.275</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>0.089</v>
       </c>
     </row>
     <row r="41">
@@ -1455,13 +1455,13 @@
         <v>1.924131</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.466</v>
+        <v>0.467</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>7.064</v>
+        <v>7.339</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>1.287</v>
+        <v>1.376</v>
       </c>
     </row>
     <row r="42">
@@ -1630,13 +1630,13 @@
         <v>2.101984</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>6.762</v>
+        <v>6.761</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.1</v>
+        <v>0.825</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.609</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="49">
@@ -2057,10 +2057,10 @@
         <v>0</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>7.404</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>5.371</v>
       </c>
     </row>
     <row r="65">
@@ -2198,10 +2198,10 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>0.013882</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.015746</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>0.013882</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.015746</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0</v>
@@ -2455,15 +2455,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C80" s="3" t="n">
+        <v>0.0002445813867644823</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.0001639704021865108</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -6870,7 +6866,11 @@
           <t>Current portion of capital lease obligations (note 10)</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
           <t>-</t>
@@ -18526,7 +18526,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D322" t="inlineStr"/>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E322" t="inlineStr">
         <is>
           <t>-</t>
